--- a/docs/test-plan/cases.xlsx
+++ b/docs/test-plan/cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Onboarding" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$K$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results'!$A$1:$K$226</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:K226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10925,58 +10925,1542 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
+          <t>C3-12</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Each everyday tool can be turned off on its own</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Colour, brows, beard, and nails are on</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>The owner turns one tool off and a guest requests it</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>That tool returns TOOL and the others still run after they are turned back on</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>C4-07</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>A photo over 2 MB is refused before it is decoded</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>A file larger than 2 MB</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>It is posted as the selfie</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>The API returns SIZE and does not spend a credit</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>C6-05</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Book bridal trial stores a bridal lead and a WhatsApp link</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Bridal is on and the salon has a WhatsApp number</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>The guest posts a name, a wedding date, and one look</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>A BRIDAL lead is stored and the response has a wa.me link</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>C6-06</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>A bridal trial accepts at most six looks</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Seven look ids</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>The trial is posted</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>The API returns 400</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>C9-04</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>The same bridal look is shown again without spending another try</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>A look is already in the visit cache</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>The same photo and the same selections are requested</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>The saved picture is returned and the generator is not called</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>C10-06</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>An anonymous daily cap of zero blocks the next preview</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>anonDailyCap is 0</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>A guest requests a hairstyle</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>The API returns CAP and the cap is restored to 8</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>C10-07</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>A paid preview cannot reserve a credit when the balance is zero</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>The isolation salon balance is set to 0</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>reserveCredits asks for one credit</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>It throws INSUFFICIENT and the balance stays 0</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>C11-12</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>On the way is stored on the ticket</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>A live token</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>The guest posts action way</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>onTheWay is true</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>C12-05</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>A second request for the same phone returns the open request</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>The salon is in time-request mode and one request exists</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>The same phone asks again</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>The token does not increase</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>S1-04</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Sign out drops the staff session</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Staff is signed in</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>They sign out</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>The queue desk redirects to login</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>S2-06</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Start and Done move a called guest through the chair</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>One waiting guest and a free chair</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Staff taps next, start, then done</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>The public ticket goes to IN_SERVICE and then DONE</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>S3-03</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>A walk-in can be added with no phone</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>The live line is open</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Staff adds a name and leaves the phone empty</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>The waiting card has that name and no phone</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>S3-04</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>A walk-in with a short phone is refused</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>The live line</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>The phone is 12345</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>The API returns 400</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>O1-02</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>O1</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Staff still see onboarding until the owner finishes it</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>onboardingDone is false</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Staff open the queue desk</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>The onboarding link is present, and it is gone after Finish</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>O2-05</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>GSTIN is saved and shown back</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>The owner is signed in</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>gstin is set</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>Settings returns that value</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>O3-02</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>The owner can turn groom on and back off</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Groom is off</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>productGroom is saved true, then false</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>The row follows both saves</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>O5-03</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>O5</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Zero is accepted as an anonymous cap and blocks that group</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>The owner saves anonDailyCap 0</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>A guest requests a preview</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>The save succeeds and the preview returns CAP</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>O9-04</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>O9</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>An inactive service disappears from the public join list</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>A service named Hidden Cut 505a</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>The owner marks it inactive</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>The public board no longer lists it</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>O11-03</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>O11</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Almost-your-turn minutes must be from 0 to 120</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>The live desk</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>alertLeadMin is 121, then 0</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>121 is rejected and 0 is stored</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>O15-02</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>O15</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Printing the QR on localhost is refused</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>The public URL is still this machine</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/v1/qr for the demo salon</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>The API returns LOCAL_DOMAIN</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>A2-05</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>super</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>A new salon gets a 14-day trial and a copy of the styles</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>The isolation salon was created by the super admin</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>The row and its styles are read</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>Trial end is 14 days out and every catalogue style was copied</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>db</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>A4-04</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>super</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>A credit note is stored with the adjustment</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>The super admin adjusts by 7</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>The note is launch note 505a</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>The ledger row has that note and delta 7</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>http+db</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>P1-06</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Login allows 8 attempts per email and 30 per IP in 15 minutes</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>A fresh email bucket with a limit of 8</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>The ninth attempt arrives</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>The shared limiter refuses, and the login route is wired to those two limits</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>P3-03</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Another salon's waiting guest is not on this desk</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>The isolation salon has a waiting guest named Iso Desk Only</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>QA staff load their desk</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>That name is absent</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>http+db</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>P4-03</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>The guest page does not name a model or a provider</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Mock AI</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>A guest opens the demo salon</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>The HTML has no OpenAI, gpt, or fal model name</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>X2-02</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>No-show on the desk shows on the guest ticket</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>One waiting guest and a free chair</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Staff call next and then no-show</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>The public ticket status is NO_SHOW</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>X7-02</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>X7</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>The saved brand colour is on the welcome page</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>The owner sets the primary colour</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>A guest opens the welcome page</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>That colour is in the page style</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>X9-02</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>X9</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Resuming a salon removes the paused page</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>The isolation salon is suspended</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Status returns to trial</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>The public page no longer says the salon is paused</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
           <t>X1-04</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>X1</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>cross</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>A new live token is one higher than today's max</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>The live line has a known max token</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>Another guest joins</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>Their token is max+1</t>
         </is>
       </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J198" s="2" t="inlineStr">
-        <is>
-          <t>http</t>
-        </is>
-      </c>
-      <c r="K198" s="2" t="inlineStr"/>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K198"/>
+  <autoFilter ref="A1:K226"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
